--- a/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P103_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
+++ b/results/reliability_eval/reliability_eval_09-03-1/Llama-3-8B_P103_neg1_sample_15_tokens_0.1_temp_direct_answer_scores_09-03-1.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.4947732900860435</v>
+        <v>0.5760268370358863</v>
       </c>
       <c r="B2" t="n">
-        <v>0.8486241418652098</v>
+        <v>0.8616865173027011</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4947729550781172</v>
+        <v>0.5760268370358863</v>
       </c>
       <c r="D2" t="n">
-        <v>0.848624500736185</v>
+        <v>0.8616865173027011</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5061556031415703</v>
+        <v>0.4235189917663508</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8524127388315546</v>
+        <v>0.8179860805561486</v>
       </c>
       <c r="G2" t="n">
-        <v>0.997102348941576</v>
+        <v>0.9993063538915644</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9993914823434928</v>
+        <v>0.9998361607109759</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8534288638689866</v>
+        <v>0.8393039918116684</v>
       </c>
     </row>
   </sheetData>
